--- a/artfynd/A 22663-2024 artfynd.xlsx
+++ b/artfynd/A 22663-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128512662</v>
       </c>
       <c r="B2" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128512656</v>
       </c>
       <c r="B3" t="n">
-        <v>80148</v>
+        <v>80152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128512660</v>
       </c>
       <c r="B4" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128512663</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22663-2024 artfynd.xlsx
+++ b/artfynd/A 22663-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128512662</v>
       </c>
       <c r="B2" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22663-2024 artfynd.xlsx
+++ b/artfynd/A 22663-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128512662</v>
       </c>
       <c r="B2" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128512656</v>
       </c>
       <c r="B3" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128512660</v>
       </c>
       <c r="B4" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128512663</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22663-2024 artfynd.xlsx
+++ b/artfynd/A 22663-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128512662</v>
       </c>
       <c r="B2" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22663-2024 artfynd.xlsx
+++ b/artfynd/A 22663-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128512662</v>
       </c>
       <c r="B2" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128512656</v>
       </c>
       <c r="B3" t="n">
-        <v>80154</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128512660</v>
       </c>
       <c r="B4" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128512663</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22663-2024 artfynd.xlsx
+++ b/artfynd/A 22663-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128512662</v>
       </c>
       <c r="B2" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128512656</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>80185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128512660</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128512663</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22663-2024 artfynd.xlsx
+++ b/artfynd/A 22663-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128512662</v>
       </c>
       <c r="B2" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22663-2024 artfynd.xlsx
+++ b/artfynd/A 22663-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128512662</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128512656</v>
       </c>
       <c r="B3" t="n">
-        <v>80185</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128512660</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128512663</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22663-2024 artfynd.xlsx
+++ b/artfynd/A 22663-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128512662</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128512656</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>80094</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128512660</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128512663</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22663-2024 artfynd.xlsx
+++ b/artfynd/A 22663-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128512662</v>
       </c>
       <c r="B2" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128512656</v>
       </c>
       <c r="B3" t="n">
-        <v>80094</v>
+        <v>80099</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128512660</v>
       </c>
       <c r="B4" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128512663</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
